--- a/ES/Datos/A7_A8_A9_Documented_Public_Reviews_Corpus.xlsx
+++ b/ES/Datos/A7_A8_A9_Documented_Public_Reviews_Corpus.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nube\iCloudDrive\Trabajo\GitHub\aires-pl-a7-a8-a9\ES\Datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1720F55-E04B-487F-91D2-D5E29B789166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AF20563-E41B-4FA2-8A08-0DFCCA1AABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="582">
   <si>
     <t>B6 reseñas A/B · A7 A8 A9 · una fila = una reseña · URL aparte del texto · traducir solo columnas amarillas · 107 filas · 30-09-2026 · no es denuncia</t>
   </si>
@@ -1822,6 +1822,10 @@
   </si>
   <si>
     <t>https://maps.app.goo.gl/s7C5V3uMSgTsC9dN6</t>
+  </si>
+  <si>
+    <t>Corpus documental de reseñas públicas verificables (Clasificación A/B)
+Corredores A7 · A8 · A9 | Una reseña por fila | URL de origen independiente | Actualizado: 21-10-2026 | 137 registros</t>
   </si>
 </sst>
 </file>
@@ -2171,7 +2175,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -2530,6 +2534,9 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
@@ -2865,8 +2872,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="113" t="s">
-        <v>0</v>
+      <c r="A1" s="121" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="113" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
